--- a/Excel/SceneConfig@cs.xlsx
+++ b/Excel/SceneConfig@cs.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\GitPro\GenshinGamePlay\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -50,6 +55,9 @@
     <t>场景路径</t>
   </si>
   <si>
+    <t>寻路数据</t>
+  </si>
+  <si>
     <t>是否日夜循环环境类型</t>
   </si>
   <si>
@@ -68,6 +76,9 @@
     <t>Perfab</t>
   </si>
   <si>
+    <t>NavMesh</t>
+  </si>
+  <si>
     <t>DayNight</t>
   </si>
   <si>
@@ -93,6 +104,9 @@
   </si>
   <si>
     <t>Scenes/MapScene/Sample.unity</t>
+  </si>
+  <si>
+    <t>Navmesh/Sample/Sample.bytes</t>
   </si>
   <si>
     <t>1,2,3,4</t>
@@ -1098,7 +1112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:J8"/>
+  <dimension ref="C2:K8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="21.1083333333333" style="2" customWidth="1"/>
@@ -1107,14 +1121,14 @@
     <col min="4" max="4" width="15.1083333333333" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.66666666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.775" style="2" customWidth="1"/>
-    <col min="7" max="7" width="31.4416666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="32.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.25" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="7" max="8" width="31.4416666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="32.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:10">
+    <row r="2" spans="3:11">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1124,17 +1138,17 @@
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="I2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="3:10">
+    <row r="3" spans="3:11">
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1159,82 +1173,96 @@
       <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="3:10">
+    <row r="4" spans="3:11">
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="3:10">
+    <row r="5" spans="3:11">
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" spans="3:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="1">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>23</v>
+      <c r="J6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="7:7">
+    <row r="7" spans="3:11">
       <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="7:7">
+    <row r="8" spans="3:11">
       <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
